--- a/data/real_estate_listings_raw.xlsx
+++ b/data/real_estate_listings_raw.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L41"/>
+  <dimension ref="A1:L21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -493,353 +493,365 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Bán Nhà mặt phố tại nhà số 11, Đường 13, Phường Long Bình, TP.HCM. Giá chỉ 13 tỷ, DT: 123.5m2</t>
+          <t>Bán nhà khu họ Lê - Quận Tân Phú mặt tiền Lê Niệm, 4 lầu đường 14m, khu dân trí cao. Giá 11.8 tỷ TL</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>/ban-nha-mat-pho-duong-13-phuong-long-binh-71/ban-so-11-uong-13-13-ty-123-5m2-tp-hcm-pr45176664</t>
+          <t>/ban-nha-mat-pho-duong-le-niem-phuong-phu-thanh-70/ban-khu-ho-tan-tien-nem-o-to-tranh-nhau-full-cong-nang-khu-dan-tri-cao-pr45624795</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>13 tỷ</t>
+          <t>11,8 tỷ</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>123,5 m²</t>
+          <t>67 m²</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>105,26 tr/m²</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
+          <t>176,12 tr/m²</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>·</t>
+          <t>Q. Tân Phú (P. Phú Thạnh mới)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Nhanh tay sở hữu Nhà mặt phố tại Nhà số 11, Đường 13, Phường Long Bình, Hồ Chí Minh (địa chỉ cũ: Thành phố Thủ Đức, Hồ Chí Minh) với diện tích 123.5m², giá chỉ 13 tỷ. Đây là một cơ hội tuyệt vời cho những ai muốn đầu tư hoặc định cư tại khu vực sôi động này.- Diện tích: 123.5m²  - Giá: 13 tỷ VND  - Pháp lý đầy đủ, sổ đỏ  - Chiều ngang mặt tiền: 5m, dài 26m, rất thích hợp cho kinh doanh  - Chiều rộng mặt đường khoảng 20m, phù hợp cho xe hơi vào th...</t>
+          <t>Bán nhà khu họ Lê - Tân Phú - Mặt tiền Lê Niệm ô tô tránh nhau, full công năng khu dân trí cao.Căn nhà tọa lạc trên đường Lê Niệm, khu dân cư hiện hữu, an ninh, phù hợp cho gia đình sinh sống lâu dài. Đường rộng ô tô tránh nhau thoải mái, di chuyển thuận tiện.Diện tích 67m², kết cấu 1 trệt 3 lầu sân thượng, gồm 4 phòng ngủ, 6 WC, bố trí tối ưu công năng, đáp ứng nhu cầu ở cho gia đình đông người.Không gian nhà thoáng, tiện nghi đầy đủ, có thể dọn...</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>‎Doan Trang</t>
+          <t>‎Viết Ân Luxury</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0339 520 *** · Hiện số</t>
+          <t>0965 221 *** · Hiện số</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>['https://file4.batdongsan.com.vn/crop/562x284/2026/02/24/20260224160106-b140_wm.jpg', 'https://file4.batdongsan.com.vn/crop/283x141/2026/02/24/20260224160109-6312_wm.jpg', 'https://file4.batdongsan.com.vn/crop/140x140/2026/02/24/20260224160112-db6c_wm.jpg', 'https://file4.batdongsan.com.vn/crop/140x140/2026/02/24/20260224160114-b432_wm.jpg']</t>
+          <t>['https://file4.batdongsan.com.vn/crop/348x174/2026/04/25/20260425085205-d9c7_wm.jpg', 'https://file4.batdongsan.com.vn/crop/115x86/2026/04/25/20260425085205-c78d_wm.jpg', 'https://file4.batdongsan.com.vn/crop/115x86/2026/04/25/20260425085205-0c36_wm.jpg', 'https://file4.batdongsan.com.vn/crop/115x86/2026/04/25/20260425085205-c7fb_wm.jpg', 'https://file4.batdongsan.com.vn/resize/200x200/2025/11/10/20251110142947-2fbc.jpg']</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Nhà mới full nội thất Phú Nhuận - 3PN - 2 mặt tiền hẻm - vào ở ngay</t>
+          <t>Bán nhanh trong tháng chỉ 16tỷ9 ngay mặt tiền doanh thu 90tr/tháng</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>/ban-nha-rieng-duong-co-giang-phuong-2-21-68/o-p-2-phu-nhuan-dep-don-tet-32m2-2-mat-tien-pr45027406</t>
+          <t>/ban-nha-mat-pho-duong-nguyen-thuong-hien-phuong-6-13-66/ban-can-ho-dich-vu-tien-doanh-thu-90tr-thang-pr45286134</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>5,2 tỷ</t>
+          <t>16,9 tỷ</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>32 m²</t>
+          <t>90 m²</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>162,5 tr/m²</t>
+          <t>187,78 tr/m²</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Phú Nhuận, Hồ Chí Minh</t>
+          <t>Q. Bình Thạnh (P. Bình Lợi Trung mới)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Bán nhà Phú Nhuận, hẻm Cô Giang. Diện tích đất 32m², diện tích sử dụng ~60m². Nhà mới xây, 1 trệt 1 lầu, 3 phòng ngủ 2 vệ sinh. 2 mặt tiền hẻm, nhà rất thoáng, sân để 3 xe máy. Bán nguyên căn full nội thất: Máy lạnh, giường tủ, bếp, tủ lạnh, tivi, cây xanh. Chỉ cần xách vali vào ở, không phát sinh chi phí. Khu dân cư an ninh, gần trung tâm. Sổ hồng riêng, pháp lý rõ ràng. Giá 5.2 tỷ thương lượng mạnh cho khách thiện chí. Liên hệ ngay 0934 607 *** -...</t>
+          <t>Bán tòa nhà 2 mặt tiền (trước sau) bao gồm 1 mặt bằng kinh doanh riêng biệt và 11 CHDV. DT 4,1x19 (hậu 5,55) = 90m² công nhận 66m², đúc 4 tấm dòng tiền trên 90tr/ tháng.Hệ thống PCCC đầy đủ, thang may, ban công sân vườn... Giá bán 16.9 tỷ (bớt lộc).</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>‎Kiet Tran</t>
+          <t>‎Nguyễn Hữu Thế</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0934 607 *** · Hiện số</t>
+          <t>0906 844 *** · Hiện số</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>['https://file4.batdongsan.com.vn/crop/348x174/2026/01/14/20260114154758-ac64_wm.jpg', 'https://file4.batdongsan.com.vn/crop/115x86/2026/01/14/20260114154758-20ad_wm.jpg', 'https://file4.batdongsan.com.vn/crop/115x86/2026/01/14/20260114154758-b9fa_wm.jpg', 'https://file4.batdongsan.com.vn/crop/115x86/2026/01/14/20260114154757-1e46_wm.jpg']</t>
+          <t>['https://file4.batdongsan.com.vn/crop/348x174/2026/03/11/20260311202036-7c57_wm.jpg', 'https://file4.batdongsan.com.vn/crop/115x86/2026/03/11/20260311202036-719e_wm.jpg', 'https://file4.batdongsan.com.vn/crop/115x86/2026/03/11/20260311202036-2a30_wm.jpg', 'https://file4.batdongsan.com.vn/crop/115x86/2026/03/11/20260311202036-7d9d_wm.jpg', 'https://file4.batdongsan.com.vn/resize/200x200/2024/09/26/20240926173036-97f6.jpg']</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Bán nhà hẻm Lý Thường Kiệt, P8, Tân Bình nhà hẻm lớn giá tốt khu vực liên hệ chủ</t>
+          <t>Bán nhà chính chủ Bình Hưng Hòa B, Q. Bình Tân, 1 trệt lửng 3 lầu, tặng full nội thất cao cấp</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>/ban-nha-rieng-pho-ly-thuong-kiet-phuong-8-14-69/ban-hem-p8-tan-binh-hem-lon-gia-tot-khu-vuc-lien-he-chu-pr45129947</t>
+          <t>/ban-nha-rieng-duong-so-2-phuong-binh-hung-hoa-b-65/ban-chinh-chu-q-tan-1-tret-lung-3-lau-tang-full-noi-that-cao-cap-pr45541874</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2,89 tỷ</t>
+          <t>6,85 tỷ</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>17,75 m²</t>
+          <t>65,4 m²</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>162,82 tr/m²</t>
+          <t>104,74 tr/m²</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Tân Bình, Hồ Chí Minh</t>
+          <t>Q. Bình Tân (P. Bình Tân mới)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Bán nhà hẻm 373/182/9 Lý Thường Kiệt, P8, Tân Bình. Hẻm trước nhà 4m. Cách MT 5 căn. Hẻm thông gần chợ ông Hoàng. Diện tích: 2,5m x 7,1m (cn 17.1m²). Trệt, 1 lầu đúc giả, 2wc.Giá chào 2,89 tỷ bớt Lộc. Liên hệ: 0785 028 *** 0909 584 *** My.</t>
+          <t>Nhà chính chủ sở hữu vị trí: Bình Hưng Hòa B, Quận Bình Tân khu dân cư an ninh, thuận tiện di chuyển các quận trung tâm.Thông tin chi tiết: + Diện tích: 4m x 16.5m (65.4m²). + Kết cấu: 1 trệt + lửng + 3 lầu. Công năng: + 4 phòng ngủ rộng rãi. + 1 phòng thờ riêng. + 1 phòng xông hơi (thiết kế sẵn, chỉ cần hoàn thiện). + Tặng full nội thất 3 phòng dọn vào ở ngay.Ưu điểm nổi bật: Nhà mới, thiết kế hiện đại, tối ưu không gian. Phù hợp gia đình đông n...</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>‎My</t>
+          <t>‎Chuyên Bất Động Sản Siêu Ngộp Tphcm - Vùng Ven</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0909 584 *** · Hiện số</t>
+          <t>0775 587 *** · Hiện số</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['https://file4.batdongsan.com.vn/crop/348x174/2026/04/13/20260413161417-8fb4_wm.jpg', 'https://file4.batdongsan.com.vn/crop/115x86/2026/04/13/20260413160537-dc8a_wm.jpg', 'https://file4.batdongsan.com.vn/crop/115x86/2026/04/13/20260413160537-69da_wm.jpg', 'https://file4.batdongsan.com.vn/crop/115x86/2026/04/13/20260413160537-42d6_wm.jpg', 'https://file4.batdongsan.com.vn/resize/200x200/2026/04/13/20260413162608-4e6e.jpg']</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Bán NR tại Trần Xuân Soạn, chỉ còn 26 tỷ, 173m2, chính chủ, uy tín</t>
+          <t>Nhà phố hiện đại, xây dựng tâm huyết - Hẻm 41 Chuyên Dùng Chín Q7 - 4m x 15m Giá 7,45 tỷ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>/ban-nha-rieng-pho-tran-xuan-soan-phuong-tan-hung-14-59/ban-nr-tai-27-ty-180m2-chinh-chu-uy-tin-pr42599412</t>
+          <t>/ban-nha-rieng-duong-chuyen-dung-9-phuong-phu-my-9-59/pho-hien-dai-4-tang-hem-3-5m-chinh-q7-dt-4m-x-16m-gia-7-49-ty-pr41685836</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>26 tỷ</t>
+          <t>7,45 tỷ</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>173 m²</t>
+          <t>61,5 m²</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>150,29 tr/m²</t>
+          <t>121,14 tr/m²</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Quận 7, Hồ Chí Minh</t>
+          <t>Quận 7 (P. Phú Thuận mới)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Nhà riêng tại Trần Xuân Soạn, Quận 7, Hồ Chí Minh, với diện tích 173m², DT sàn: 308m². Xe tải đậu trước cửa, xe hơi ngủ trong nhà 4 tầng, 5PN, 4WC, pháp lý đầy đủ. - Ngõ vào rộng 6m, thuận tiện cho xe hơi. - Mặt tiền 7.4m, phù hợp kinh doanh. - Nội thất đầy đủ, sẵn sàng để ở hoặc cho thuê. - Hướng cửa chính và ban công đều Đông, đón gió mát. Đặc biệt, gần cầu Nguyễn Khoái bắt qua Q4 đã khởi công dự báo bds khu này sẽ tăng giá mạnh.Gần các trường ...</t>
+          <t>Nhà Phố hiện đại đầy đủ nội thất hẻm 3,5m 41 Chuyên Dùng Chín Phường Phú Mỹ Quận 7 (Cách Phú Mỹ Hưng 500m, thông Huỳnh Tấn Phát, Phạm Hữu Lầu). - Diện tích: 4m x 15m. CN 61,5m² - Đất đô thị 57.5m² - đất trồng cây phần lộ giới là 3,9m². - 01 trệt 02 lầu 01 sân thượng 04 phòng ngủ, 05 WC - Đúc kiên cố chắc chắn, đủ nội thất cao cấp, gara xe, phòng khách, bếp, phòng thờ đầy đủ công năng. - Sân để xe, hẻm trước nhà thoáng mát... - Khu dân cư an ninh,...</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>‎Tom Bui</t>
+          <t>‎Nguyễn Chí Quang Huy</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0905 335 *** · Hiện số</t>
+          <t>0988 999 *** · Hiện số</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['https://file4.batdongsan.com.vn/crop/348x174/2026/01/12/20260112083541-7673_wm.jpg', 'https://file4.batdongsan.com.vn/resize/200x200/2025/12/12/20251212152104-848c.jpg']</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Bán nhà 85/112/42 đường Bình Thành, ngang 14m, 4 tấm, đường 8m</t>
+          <t>Giảm 1 tỷ biệt thự cao cấp 10,5m x 18m (189m²) compound Liên Phường liền kề Global City Đỗ Xuân Hợp</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>/ban-nha-rieng-duong-binh-thanh-phuong-binh-hung-hoa-b-65/ban-85-112-42-ngang-14m-4-tam-8m-pr45118179</t>
+          <t>/ban-nha-biet-thu-lien-ke-phuong-phuoc-long-b-hung-phu-2/gap-ban-cao-cap-compound-global-city-o-xuan-hop-pr45392180</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>7,5 tỷ</t>
+          <t>24 tỷ</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>77,2 m²</t>
+          <t>189 m²</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>97,15 tr/m²</t>
+          <t>126,98 tr/m²</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Bình Tân, Hồ Chí Minh</t>
+          <t>Quận 9 (P. Phước Long mới)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Bán nhà 85/112/42 Bình Thành, phường Bình Tân. DT ngang 14m x dài 10m (cạnh còn lại 2,36m). Tổng DT đất 77,2m², tổng DT sàn 284m². Xây 3,5 tấm. 5 phòng ngủ, 6 WC, 1 gara xe hơi riêng, 1 phòng khách, 1 phòng bếp, 1 phòng thờ, sân thượng, có bancol. Đường nhựa 8m có lề đường, ngay công viên. Nội thất deco full, 6 máy lạnh.Giá 7,5 tỷ có thương lượng. LH 0988 844 ***.</t>
+          <t>Cơ hội hiếm để sở hữu biệt thự đẳng cấp ngay trung tâm khu Đông, nơi đang bùng nổ hạ tầng và giá trị bất động sản.Vị trí chiến lược: Nằm trong khu dân cư compound Liên Phường, khu vực dân trí cao, đồng bộ. Liền kề Global City, đại đô thị chuẩn quốc tế đang phát triển mạnh. Cách công viên chỉ 30m, không gian sống xanh, thoáng. Cách Global City chỉ 500m. Gần vòng xoay Liên Phường chưa đến 300m, kết nối giao thông cực kỳ thuận tiện. Đón đầu tuyến Me...</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>‎Dũng Nhà Đất Mặt Tiền - Kho Xưởng</t>
+          <t>‎Trọng Quý</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0988 844 *** · Hiện số</t>
+          <t>0945 438 *** · Hiện số</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>['https://file4.batdongsan.com.vn/resize/200x200/2019/02/27/20190227173913-dc8e.jpg']</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Mình chính chủ cần bán nhà riêng - Thạnh Xuân 33 - HXH - 4.7tỷ</t>
+          <t>Siêu hiếm! Nhà thổ cư DT lớn vị trí vàng TT quận Tân Bình giá cực tốt</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>/ban-nha-rieng-duong-thanh-xuan-33-phuong-thoi-an-1-64/minh-chinh-chu-can-ban-xuan33-hxh-nhinh4ty-pr45109121</t>
+          <t>/ban-nha-rieng-duong-truong-chinh-phuong-14-10-69/sieu-hiem-tho-cu-dt-lon-vi-tri-vang-tt-quan-tan-binh-gia-cuc-tot-pr45615165</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>4,7 tỷ</t>
+          <t>28,5 tỷ</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>56 m²</t>
+          <t>227,23 m²</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>83,93 tr/m²</t>
+          <t>125,42 tr/m²</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Quận 12, Hồ Chí Minh</t>
+          <t>Q. Tân Bình (P. Tân Bình mới)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>+ Nhà kết cấu 2 tầng BTCT, 2PN khép kín, 3WC, giếng trời, phòng khách lớn, bếp rộng rãi. Nhà cứng cáp, thêm thùng sơn nhà đẹp như mới. + Diện tích: 4 x 14m sổ công nhận 56m². + Khu dân cư đồng bộ, dân trí, an ninh, hàng xóm thân thiện. + Hẻm rộng 6m thông khắp nơi, sạch sẽ, khu vực đang phát triển mạnh. + Pháp lý: Sổ vuông đẹp, hoàn công đủ pháp lý chuẩn, công chứng ngay.</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+          <t>Một BĐS hiếm hoi còn sót lại ngay lõi trung tâm phù hợp nhà ở, làm văn phòng, hoặc đầu tư dài hạn. * DT lớn: Ngang 11m x dài 21m. CN 227.23m². * Thế đất đẹp, vuông vức cực kỳ lý tưởng xây nhà phố cao cấp hoặc biệt thự villa. * Nằm trong khu compound riêng biệt chỉ 6 căn, xung quanh là villa biệt thự liền kề. * Môi trường sống an ninh, yên tĩnh, dân trí cao.Vị trí vàng - đắc địa. * Nằm trên trục đường Trường Chinh, tuyến đường huyết mạch kết nối t...</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>‎Huynhquangvinh</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0908 360 *** · Hiện số</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>[]</t>
@@ -849,101 +861,109 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Chủ gấp bán - Thạnh Lộc 19 - 50.5m2 - thương lượng</t>
+          <t>Chính chủ bán nhà riêng, khu dân cư yên tĩnh, khép kính, dân trí cao, phù hợp để ở, tích trữ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>/ban-nha-rieng-duong-thanh-loc-19-1-phuong-thanh-loc-3-64/chu-gap-ban-loc19-60-5m2-thuong-luong-pr45071210</t>
+          <t>/ban-nha-rieng-duong-xuan-thoi-thuong-22-xa-xuan-thoi-thuong-75/chinh-chu-ban-khu-dan-cu-yen-tinh-khep-kinh-dan-tri-cao-phu-hop-e-o-tich-tru-pr45435272</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>4,6 tỷ</t>
+          <t>4,5 tỷ</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>50,5 m²</t>
+          <t>80,1 m²</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>91,09 tr/m²</t>
+          <t>56,18 tr/m²</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Quận 12, Hồ Chí Minh</t>
+          <t>H. Hóc Môn (X. Bà Điểm mới)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>+ Vị trí: ĐH Nguyễn Tất Thành CS APĐ, THPT Thạnh Lộc, THCS THPT Trần Cao Vân, BHX, chợ, bến xe ngã tư Ga,... + Kết nối nhanh đến các đường lớn Hà Huy Giáp, Đỗ Mười, Nguyễn Oanh,... + Kết cấu: 1 trệt, 1 lầu, phòng khách, bếp, 3 phòng ngủ, 2 nhà vệ sinh, có giếng trời,... + Diện tích: 4x12,5m. + Pháp lý: Chuẩn. + Giá 4.6 tỷ.</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+          <t>Hiện mình cần bán lại căn nhà phố, gần chợ Xuân Thới Thượng, Hóc Môn.- Vị trí: Nằm trong khu dân cư khép kính, an ninh, dân cư dân trí cao, hàng xóm thân thiện, Anh/ Chị nào mua ở, cần yên tỉnh, có chỗ cho bé chơi, trồng cây thì nơi đây rất phù hợp. - Diện tích: 5.32m x 15.07m. - Nhà Xây 1 trệt, 1 lửng. - Sổ Hồng đầy đủ. - Giá bán 4,5 tỷ (khách thiện chí mua bán, nhanh gọn mình có thương lượng thêm).- Thông tin đăng thật, vị trí thật, hình ảnh th...</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>‎Nghĩa Hợp</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0936 118 *** · Hiện số</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['https://file4.batdongsan.com.vn/resize/200x200/2022/10/13/20221013163008-677c.jpg']</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>(Cực hiếm) bán nhà 2 mặt tiền 146m2 (5x28) mặt phố Tân Sơn - Xây được 8 lầu - Rẻ hơn TT 20% - HH 1%</t>
+          <t>Bán gấp nhà MT Văn Chung P. 13 DT: 4.55x36m KC: NC4 giá: 24 tỷ TL Sát nhà ga T3 GPXD: 1 hầm 6 lầu</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>/ban-nha-mat-pho-duong-tan-son-phuong-12-8-67/cuc-hiem-ban-2-tien-146m2-5x28-xay-uoc-8-lau-re-hon-tt-20-hh-1-pr45176332</t>
+          <t>/ban-nha-mat-pho-duong-van-chung-phuong-13-10-69/ban-gap-mt-p-13-dt-4-95x36-kc-nc4-gia-24-x-tl-sat-ga-t3-gpxd-1-ham-6-lau-pr45573304</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>20,5 tỷ</t>
+          <t>24 tỷ</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>146 m²</t>
+          <t>165 m²</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>140,41 tr/m²</t>
+          <t>145,46 tr/m²</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Gò Vấp, Hồ Chí Minh</t>
+          <t>Q. Tân Bình (P. Tân Bình mới)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Thông tin tài sản chính xác 100%. Siêu phẩm nhà 2 mặt tiền đường 30m tại phố Tân Sơn (giáp Tân Bình - Gò Vấp) với giá tốt hơn thị trường khoảng 20%. Có HH 1% cho ACE MG- Pháp lý: Sổ đỏ chính chủ, giao dịch ngay. Có hỗ trợ vay Bank (Định giá rất cao)- Diện tích 146m² (4,96/4,99 x 29) vuông vức, 2 mặt tiền trước sau thoáng vĩnh viễn, hẻm sau rộng ~ 2,5m- Nhà cao 2 lầu (chi phí xây dựng ~ 2 tỷ)+ Tầng trệt: Gara ô tô + Phòng Khách và Bếp siêu rộng + ...</t>
+          <t>Bán gấp nhà mặt tiền Văn Chung P. 13 vị trí siêu đẹp gần nhà ga T3.Vị trí: Mặt tiền đường Văn Chung, Phường 13 khu vực sầm uất, tiềm năng tăng giá mạnh. Cách nhà ga T3 Tân Sơn Nhất chỉ vài bước hưởng trọn lưu lượng khách cực lớn. Diện tích: 4.55m x 36m công nhận chuẩn 165m², đất đẹp vuông vức. Kết cấu: Nhà cấp 4 tiện xây mới theo nhu cầu. Đã có GPXD: 1 hầm + 6 lầu phù hợp làm CHDV, khách sạn, văn phòng, khai thác dòng tiền cao.Giá bán: 24 tỷ (còn...</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
@@ -957,155 +977,159 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bán nhà MT đường 8 XVNT, P. Bình Thạnh, ôtô ở trong nhà, khu đô thị sinh thái bán đảo Thanh Đa</t>
+          <t>MTKD Thoại Ngọc Hầu (gần Nguyễn Sơn), 4x36m, cấp 4, giá 14.9 tỷ TL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>/ban-nha-rieng-duong-xo-viet-nghe-tinh-phuong-26-66/ban-mt-uong-8-xvnt-p-binh-thanh-oto-o-trong-khu-o-thi-sinh-thai-ban-ao-thanh-a-pr45163797</t>
+          <t>/ban-nha-mat-pho-duong-thoai-ngoc-hau-phuong-phu-thanh-70/mtkd-gan-nguyen-son-4x36m-cap-4-gia-15-8-ty-tl-pr45327165</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>11,2 tỷ</t>
+          <t>14,9 tỷ</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>65 m²</t>
+          <t>138,8 m²</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>172,31 tr/m²</t>
+          <t>107,35 tr/m²</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Bình Thạnh, Hồ Chí Minh</t>
+          <t>Q. Tân Phú (P. Phú Thạnh mới)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Chính chủ cần bán nhà: * Nhà 3 tầng + sân thượng, 3PN, 1 phòng làm việc, 3WC, 1 phòng khách, nhà bếp, phòng giặt có sân để xe, ô tô ngủ trong nhà. - Nhà mới sạch đẹp, nội thất đầy đủ, dọn đồ vào ở. - Bàn giao toàn bộ đầy đủ wifi từng tầng, camera an ninh toàn bộ nhà. - DT công nhận đủ 65m², đường xe tải ra vào, có sân đậu ôtô trong nhà thông Ql13. - Xung quanh đầy đủ tiện ích, gần ngay trường HUTECH, Ngoại Thương, Giao Thông Vận Tải, Hồng Bàng......</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
+          <t>MTKD Thoại Ngọc Hầu, Quận Tân Phú. - Diện tích: 4x36m (138,8m²). - Kết cấu: Nhà cấp 4. - Gồm: 6 phòng ngủ và 6WC đang cho thuê 21 triệu/tháng. - Thích hợp vừa ở vừa kinh doanh. - Gần Siêu thị Big C. - Giá: 14.9 tỷ thương lượng. - Liên hệ: 0932 506 *** (Tân).</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>‎Nguyễn Duy Tân</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['https://file4.batdongsan.com.vn/resize/200x200/2023/12/06/20231206194434-4839.jpg']</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Đầu tư đón đầu - Góc 2 MT - 10x16.5m - 5 tầng - Giá: 19,9 tỷ - Cách UBND TP Thủ Đức chỉ 10 phút</t>
+          <t>Nhà đẹp Lê Hồng Phong - Kỳ Hòa 5x24m, nhà 5 lầu HDT 80tr/th vị trí đẹp giá 28.6 tỷ TL</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>/ban-nha-mat-pho-duong-dong-van-cong-phuong-cat-lai-khu-do-thi-cat-lai/dau-tu-don-dau-goc-2-mt-10x16-5m-5-tang-gia-19-9-ty-cach-ubnd-tp-thu-duc-chi-10-phut-pr44708079</t>
+          <t>/ban-nha-rieng-duong-le-hong-phong-phuong-12-5-62/dep-ky-hoa-5x24m-5-lau-hdt-80tr-th-vi-tri-dep-gia-28-6-ty-tl-pr43377808</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>19,9 tỷ</t>
+          <t>28,6 tỷ</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>159 m²</t>
+          <t>121 m²</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>125,16 tr/m²</t>
+          <t>236,36 tr/m²</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Quận 2, Hồ Chí Minh</t>
+          <t>Quận 10 (P. Hòa Hưng mới)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Nhà góc 2 mặt tiền - KDC Cát Lái, Tp Thủ Đức.- Diện tích lớn: 10x16,5m. Công nhận: 159m². - Kết cấu nhà mới: 5 tầng. - Nội thất full: Giường, tủ, bàn ghế, sofa, máy lạnh...- Ưu điểm: + Căn góc thoáng mát. + Gần trường THCS và Tiểu Học thuận tiện việc đưa đón con đi học. + Hạ tầng đang hoàn thiện, sắp đưa vào sử dụng như Vành Đai 3, Đường Liên Cảng giải quyết giao thông tại Cảng Cát Lái, giúp giảm tải lượng xe container vào đường Đồng Văn Cống và ...</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr"/>
+          <t>Bán nhà hẻm 10m đường Lê Hồng Phong, khu biệt thự Vườn Lan - Kỳ Hòa tập trung nhiều biệt thự, văn phòng, phòng khám,... Gần trung tâm thương mại Vạn Hạnh Mall, Hà Đô Centrosa thuận tiện sử dụng khai thác kinh doanh nhiều loại hình dịch vụ. Diện tích: 5 x 24m 121m², nhà 5 lầu nhà vị trí đẹp. Sổ hồng chính chủ thuận tiện mua bán sang tên nhanh. Giá bán: 28.6 tỷ thương lượng. Vui lòng liên hệ: 0937 865 *** Thanh Tùng để hỗ trợ xem nhà, thương lượng ...</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>‎Nguyễn Thanh Tùng</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['https://file4.batdongsan.com.vn/resize/200x200/2024/06/05/20240605160845-51a5.jpg']</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Nhà mới hẻm thông xe hơi Hoàng Bật Đạt 4x11m, 3PN + phòng thờ, giá 7.5 tỷ</t>
+          <t>Ngay ngã tư Hàng Xanh 4x20m nhà Bình Thạnh sẵn 4 tầng, hẻm 12m sát mặt tiền, vị trí kinh doanh đỉnh</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>/ban-nha-rieng-duong-hoang-bat-dat-phuong-15-8-69/moi-hem-thong-xe-hoi-4x11m-3pn-phong-tho-gia-7-5-ty-hh-1-pr45138363</t>
+          <t>/ban-nha-rieng-duong-dinh-bo-linh-phuong-24-66/ngay-nga-tu-hang-xanh-4x20m-ban-binh-thanh-4-tang-hem-12m-sat-mat-tien-vi-tri-dep-gan-q1-pr43964883</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>7,5 tỷ</t>
+          <t>12,7 tỷ</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>44 m²</t>
+          <t>80 m²</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>170,46 tr/m²</t>
+          <t>158,75 tr/m²</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Tân Bình, Hồ Chí Minh</t>
+          <t>Q. Bình Thạnh (P. Bình Thạnh mới)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Bán nhà hẻm thông xe hơi Hoàng Bật Đạt, Tân Bình. Địa chỉ: 105/ Hoàng Bật Đạt, P. 15, Q. Tân Bình (khu P. Tân Sơn mới).Kết cấu: 1 trệt 2 lầu. Gồm 3 phòng ngủ + 1 phòng thờ. 2 sân thượng trước &amp; sau, nhà thoáng, nhiều ánh sáng.Diện tích: 4 x 11m (44m²) sổ hồng riêng, công nhận đủ. Nhà xây mới, đẹp lung linh, full nội thất, dọn vào ở ngay. Hẻm thông xe hơi, xe ra vào thoải mái. Khu dân cư ở kín, an ninh, yên tĩnh.Tiện ích xung quanh đầy đủ: Gần trư...</t>
+          <t>Bán nhà 4 tầng gần ngã tư Hàng Xanh - hẻm xe hơi 12m có lề 2 bên - sát mặt tiền đường Đinh Bộ Lĩnh - vị trí ngay trung tâm cực dễ cho thuê hoặc kinh doanh.- Vị trí đẹp: Hẻm nhựa 1 trục, sát mặt tiền Đinh Bộ Lĩnh chỉ vài bước ra ngã tư Hàng Xanh. - Hẻm rộng 12m, 2 xe tải tránh nhau thoải mái giao thông thuận tiện, khu dân cư trí thức, ổn định lâu năm.- Diện tích: 4 x 20m vuông vức, không lỗi phong thủy. Công nhận 74,4m². - Kết cấu: Trệt + 2 lầu + ...</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
@@ -1119,47 +1143,47 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Mặt tiền Âu Dương Lân, 5,8x14,3m - nhà mới - ngay Tạ Quang Bửu - 3 tầng sân thượng - 24,9 tỷ</t>
+          <t>Bán nhà ngay chân cầu vượt ngã tư ga, khu đồng bộ cao tầng</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>/ban-nha-mat-pho-duong-au-duong-lan-phuong-rach-ong-60/tien-5-8x14-3m-moi-ngay-ta-quang-buu-3-tang-san-thuong-24-9-ty-pr45172012</t>
+          <t>/ban-nha-rieng-duong-thanh-loc-16-phuong-an-phu-dong-1-64/ban-ngay-chan-cau-vuot-nga-tu-ga-khu-ong-bo-cao-tang-pr45511361</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>24,9 tỷ</t>
+          <t>7,5 tỷ</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>80,1 m²</t>
+          <t>50 m²</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>310,86 tr/m²</t>
+          <t>150 tr/m²</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Quận 8, Hồ Chí Minh</t>
+          <t>Quận 12 (P. An Phú Đông mới)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Bán nhà mặt tiền đường Âu Dương Lân, Phường Chánh Hưng, Quận 8 - tương lai QH thành góc 2 mặt tiền.- Diện tích đất: 5.78m x 14,27m - 80,1m². - Diện tích sàn: 230,8m². - Hiện trạng: 3 tầng, sân thượng. - Giá: 28 tỷ giảm về 24,9 tỷ. - Hướng: Tây Nam. - Vị trí: Mặt tiền thông thoáng, ngay Tạ Quang Bửu kinh doanh sầm uất.</t>
+          <t>Nhà 5 tầng, khu văn minh xây dựng đồng bộ, hẻm thẳng rộng 12 mét có vỉa hè. Vị trí ngay chân cầu vượt ngã tư ga đi qua gò vấp 5 phút. Diện tích 4,3*12 - 1 trệt, 1 lửng, 3 lầu, 4 phòng ngủ 5 WC, full nội thất, chỉ cần mang vali vào ở. Liên hệ chính chủ 0932 038 ***. Sổ hồng để tủ.</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
@@ -1173,27 +1197,27 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chính chủ bán căn nhà tâm huyết tại trung tâm thị trấn Hóc Môn (có thương lượng)</t>
+          <t>Góc đẹp ngay Tân Chánh Hiệp xe oto đỗ cửa (không lộ giới)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>/ban-nha-rieng-duong-le-loi-1-thi-tran-hoc-mon-75/chinh-chu-can-ban-hxh-ngay-bung-binh-trung-tam-hanh-chinh-co-thuong-luong-pr44762633</t>
+          <t>/ban-nha-rieng-duong-lam-thi-ho-phuong-tan-chanh-hiep-1-64/goc-ep-ngay-xe-oto-o-cua-khong-lo-gioi-pr45667540</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>5 tỷ</t>
+          <t>6,7 tỷ</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>86,2 m²</t>
+          <t>59 m²</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>58 tr/m²</t>
+          <t>113,56 tr/m²</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1203,17 +1227,17 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Hóc Môn, Hồ Chí Minh</t>
+          <t>Quận 12 (P. Trung Mỹ Tây mới)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Chính chủ bán căn nhà tâm huyết tại thị trấn Hóc Môn.Vì nhu cầu thay đổi chỗ ở nên gia đình tôi cần bán lại căn nhà đã gắn bó nhiều năm, xây dựng chắc chắn và chăm chút kỹ lưỡng để ở lâu dài. Nhà nằm ngay trung tâm thị trấn Hóc Môn, trong hẻm thông nhiều hướng, ô tô có thể chạy vào tận cửa. Khu dân cư yên tĩnh, hàng xóm thân thiện, an ninh tốt. Từ nhà di chuyển ra chợ, trường học, ngân hàng, trung tâm hành chính chỉ vài bước chân.Diện tích đất: 8...</t>
+          <t>Bán căn góc Q12 kết cấu cực đẹp. 1 căn duy nhất xem nhà thích ngay. * Góc 2 mặt tiền hẻm 8m. Đoạn giao giữa(Huỳnh Thị Hai + Lâm Thị Hố), P. Tân Chánh Hiệp, Q 12. * DT 5x13m 59m² (không lộ giới). 1 trệt 2 lầu sân thượng 4 PN, 5WC. - Vị trí ở, buôn bán hàng online cực vip. Xe oto đậu trước nhà 2 - 3 chiếc thoải mái. * Giảm 500 tr còn 6 tỷ 700 tr.</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
@@ -1227,47 +1251,47 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Siêu phẩm mặt tiền 36 Đỗ Công Tường, Tân Phú - MT 16m cực hiếm - thu nhập 18tr/tháng - chỉ 9 tỷ</t>
+          <t>Chính chủ bán nhà hẻm Q. Bình Tân, diện tích 204.4m2, có 6 phòng trọ cho thuê, dòng tiền 20 tr/th</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>/ban-nha-mat-pho-duong-do-cong-tuong-phuong-tan-quy-2-70/sieu-pham-tien-36-o-phu-mt-16m-cuc-hiem-thu-nhap-18tr-thang-chi-9-ty-pr45167256</t>
+          <t>/ban-nha-rieng-duong-huong-lo-3-phuong-binh-hung-hoa-65/ban-hem-q-tan-dien-tich-204-4-m2-pr44488836</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>9 tỷ</t>
+          <t>9,9 tỷ</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>86 m²</t>
+          <t>204,4 m²</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>104,65 tr/m²</t>
+          <t>48,43 tr/m²</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Tân Phú, Hồ Chí Minh</t>
+          <t>Q. Bình Tân (P. Bình Hưng Hòa mới)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Bán nhà mặt phố 36 Đỗ Công Tường, 9 tỷ, 86m², 3PN, 4WC.Nhà mặt phố tại 36 Đỗ Công Tường, đường Đỗ Công Tường, Phường Tân Sơn Nhì, Hồ Chí Minh (địa chỉ cũ: Quận Tân Phú, Hồ Chí Minh) là cơ hội vàng cho những ai tìm kiếm không gian sống và kinh doanh lý tưởng. Với diện tích 86m², nhà có 1 tầng, 3PN và 4WC, phù hợp cho gia đình hoặc đầu tư cho thuê.+ Giá bán: 9 tỷ VND. + Hướng cửa chính: Nam. + Mặt tiền rộng 16m, thuận lợi cho việc kinh doanh và cho...</t>
+          <t>Nhà hẻm 2 sẹc, diện tích 204,4m², có 6 phòng trọ cho thuê với dòng tiền 20 triệu/tháng. Ngang 12 x 17m. Nội thất y như hình (nếu để lại + thêm 200 triệu). Nhà đã sửa sang mới để ở. Hẻm của đường Hương Lộ 3. Bán theo đơn giá đất 52 triệu/m².</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
@@ -1281,47 +1305,47 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Bán nhà mặt tiền Lê Đức Thọ, 8x25m CN 160m2 đúc 1T5L giá 40 tỷ</t>
+          <t>Nhà Phan Huy Ích HXH 2 lầu nội thất mới</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>/ban-nha-mat-pho-duong-le-duc-tho-phuong-6-14-67/ban-tien-8x25-cn-160m-1t5l-gia-42-5-ty-pr44897106</t>
+          <t>/ban-nha-rieng-duong-phan-huy-ich-phuong-12-8-67/hxh-2-lau-noi-that-moi-pr45664120</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>40 tỷ</t>
+          <t>2,9 tỷ</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>200 m²</t>
+          <t>17 m²</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>200 tr/m²</t>
+          <t>170,59 tr/m²</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Gò Vấp, Hồ Chí Minh</t>
+          <t>Q. Gò Vấp (P. An Hội Tây mới)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Nhà mặt phố Lê Đức Thọ, P. 6, Q. Gò Vấp, TP. HCM, với diện tích 200m²: 8x25m đúc 1T5L: Thiết kế của nhà gồm 22PN + 22WC, thích hợp làm vp công ty, căn hộ dịch vụ, toà nhà vp.. Điểm nổi bật: + Giá: 40 tỷ. + Pháp lý đầy đủ. + Phong thủy tốt, thuận lợi cho việc kinh doanh và sinh sống. Xung quanh có nhiều tiện ích: + Cách trường học: 500m. + Cách chợ/siêu thị Lotte 500m. + Cách công viên: 500m. Liên hệ để được tư vấn miễn phí qua số điện thoại 09333...</t>
+          <t>Bán nhà SHR Phan Huy Ích hẻm ô tô tận cửa cách hẻm xe tải 20m. Kết cấu 1 trệt 2 lầu đầy đủ công năng cho gia đình nhỏ. Mỗi tầng đều có ban công và có sân thượng chill chill. Vị trí nhà gần trường học các cấp và siêu thị Emart. DT 17m². DTCN 15m² LH 0937 781 ***.</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
@@ -1335,81 +1359,85 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Bán gấp biệt thự Vip nhất ngay trung tâm công viên Hoà Bình, có thưởng cho người giới thiệu</t>
+          <t>Nguyễn Văn Trỗi - khu văn phòng vip - 68m2 - ngang 7m - 6 tầng - 12 PN, WC riêng - 13,5 tỷ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>/ban-nha-biet-thu-lien-ke-duong-so-10-phuong-10-8-cityland-park-hills/ban-gap-vip-nhat-ngay-trung-tam-cong-vien-hoa-binh-co-thuong-cho-nguoi-gioi-thieu-pr45144241</t>
+          <t>/ban-nha-rieng-duong-nguyen-van-troi-phuong-15-7-68/khu-phong-vip-70m2-ngang-7m-6-tang-12-pn-wc-13-5-ty-pr45584221</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>59,99 tỷ</t>
+          <t>13,5 tỷ</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>230 m²</t>
+          <t>68 m²</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>260,83 tr/m²</t>
+          <t>198,53 tr/m²</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Gò Vấp, Hồ Chí Minh</t>
+          <t>Q. Phú Nhuận (P. Cầu Kiệu mới)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Người nhà cần bán gấp căn biệt thự tại Cityland Gò Vấp. Chỉ cặp căn duy nhất số nhà đẹp, toạ lạc ngay trung tâm công viên Hoà Bình. Hướng mát mẻ cả ngày. Phong thuỷ tốt, thịnh vượng. Diện tích: 10x23m. Có thưởng cho người giới thiệu khách mua.</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr"/>
+          <t>Nguyễn Văn Trỗi - khu văn phòng vip - 68m² - ngang 7m - 6 tầng - 12 PN, WC riêng - 13,5 tỷ.- Ngay tuyến đường Nguyễn Văn Trỗi, nối từ Q1 đi sân bay Tân Sơn Nhất. - Diện tích: 68m² | ngang 7m x dài 10m | chuẩn A4. - Kết cấu: 6 tầng, có chỗ lắp thang máy, 12PN, 12 WC riêng biệt. - Khu vực vàng cho dòng CHDV, cải tạo làm CHDV cao cấp cho dân văn phòng, Khu cao ốc văn phòng, ngân hàng, an ninh dân trí cực cao. 0979 686 *** Duy Huỳnh.</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>‎Lê Huỳnh Duy</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['https://file4.batdongsan.com.vn/resize/200x200/2025/12/17/20251217090830-da98.jpg']</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Nhà phố hiện đại, xây dựng tâm huyết - Hẻm 41 Chuyên Dùng Chín Q7 - 4m x 15m Giá 7,45 tỷ</t>
+          <t>Em villa mini ngang gần 10m hiếm có tại Bình Tân - full nội thất, chỉ cần xách vali vào ở ngay</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>/ban-nha-rieng-duong-chuyen-dung-9-phuong-phu-my-9-59/pho-hien-dai-4-tang-hem-3-5m-chinh-q7-dt-4m-x-16m-gia-7-49-ty-pr41685836</t>
+          <t>/ban-nha-rieng-duong-so-2-phuong-binh-hung-hoa-b-65/em-villa-mini-ngang-gan-10m-hiem-co-tai-tan-full-noi-that-chi-can-xach-vali-vao-o-ngay-pr45542438</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>7,45 tỷ</t>
+          <t>6,8 tỷ</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>61,5 m²</t>
+          <t>86 m²</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>121,14 tr/m²</t>
+          <t>79,07 tr/m²</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1419,1162 +1447,198 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Quận 7, Hồ Chí Minh</t>
+          <t>Q. Bình Tân (P. Bình Tân mới)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Nhà Phố hiện đại đầy đủ nội thất hẻm 3,5m 41 Chuyên Dùng Chín Phường Phú Mỹ Quận 7 (Cách Phú Mỹ Hưng 500m, thông Huỳnh Tấn Phát, Phạm Hữu Lầu). - Diện tích: 4m x 15m. CN 61,5m² - Đất đô thị 57.5m² - đất trồng cây phần lộ giới là 3,9m². - 01 trệt 02 lầu 01 sân thượng 04 phòng ngủ, 05 WC - Đúc kiên cố chắc chắn, đủ nội thất cao cấp, gara xe, phòng khách, bếp, phòng thờ đầy đủ công năng. - Sân để xe, hẻm trước nhà thoáng mát... - Khu dân cư an ninh,...</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>‎Nguyễn Chí Quang Huy</t>
-        </is>
-      </c>
+          <t>Cơ hội sở hữu nhà Bình Tân ngang lớn hiếm có phù hợp ở gia đình + đầu tư giữ tài sản. Thiết kế hiện đại full nội thất cao cấp dọn vào ở ngay. + Nhà hướng: Tây. + Diện tích: Ngang 9m34 (nở hậu 9m7)Dài 8m68. DT đất: 86m². DT xây dựng: 231m². + Kết cấu: Trệt + 3 lầu, xây dựng BTCT kiên cố. Gara ô tô trong nhà &amp; sân ngoài rộng rãi. Phòng khách sang trọng. Bếp hiện đại, thoáng. 4 phòng ngủ, 4 WC. Phòng giặt + phòng thờ riêng. Sân phơi thoáng mát. + Vị...</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>['https://file4.batdongsan.com.vn/resize/200x200/2025/12/12/20251212152104-848c.jpg']</t>
+          <t>[]</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Nhà đường nhựa 16m vị trí đẹp view thoáng có thang máy Gara ô tô ngang 5m dài 18m</t>
+          <t>Bán nhà mặt phố tại đường Số 9, Thảo Điền, 36,8 tỷ, 99m2, giá thực, gặp chủ trục tiếp</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>/ban-nha-rieng-duong-d4-phuong-phu-my-9-59/nhua-16m-vi-tri-dep-view-thoang-co-thang-may-gara-o-to-ngang-5-dai-18-pr44551437</t>
+          <t>/ban-nha-mat-pho-duong-so-9-phuong-thao-dien-1-71/ban-tai-uong-9-ien-36-8-ty-99m2-gia-thuc-gap-chu-truc-tiep-pr45631088</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>17,9 tỷ</t>
+          <t>36,8 tỷ</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>90 m²</t>
+          <t>99 m²</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>198,89 tr/m²</t>
+          <t>371,72 tr/m²</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Quận 7, Hồ Chí Minh</t>
+          <t>TP. Thủ Đức (P. An Khánh mới)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Nhà mới hoàn thiện đường nhựa 16m. - 5x18m, nhà 4 tầng thang máy 450kg. - 4 phòng nhà vệ sinh riêng từng phòng, 1 phòng thờ. - Diện tích sàn 234,2m². - Sổ hồng hoàn công pháp lý chuẩn chỉnh. - Khu dân cư đồng bộ. - Vài bước chân là công viên bờ sông, siêu thị đầy đủ tiện ích. - Cách Phú Mỹ Hưng chỉ 900m. - Tặng full nội thất trong nhà chủ về chỉ dọn vào ở. - Giá: 17,9 tỷ bớt lộc.</t>
+          <t>Bán nhà mặt phố tại đường Số 9, Phường Thảo Điền, giá 36,8 tỷ, diện tích 99m², chính chủ hot!Nhanh tay sở hữu căn nhà mặt phố tuyệt đẹp tại đường Số 9, Phường An Khánh, Hồ Chí Minh - Thành phố Thủ Đức, Hồ Chí Minh cũ với những đặc điểm nổi bật như sau:- Diện tích đất 99m², diện tích sử dụng 250m². 3 tầng, 5PN, 4WC. - Mặt tiền rộng 6,3m, đường 8m. - Pháp lý đầy đủ, sổ hồng.Ưu điểm: - Không gian sống lý tưởng, phù hợp cho gia đình hoặc kinh doanh. ...</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>‎Điền Trần</t>
+          <t>‎Trần Hữu Tùng</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>['https://file4.batdongsan.com.vn/resize/200x200/2025/09/04/20250904155050-3b73.jpg']</t>
+          <t>['https://file4.batdongsan.com.vn/crop/232x186/2026/04/26/20260426154324-f24e_wm.jpg', 'https://file4.batdongsan.com.vn/crop/115x64/2026/04/26/20260426154337-2f03_wm.jpg', 'https://file4.batdongsan.com.vn/crop/115x64/2026/04/26/20260426154353-77da_wm.jpg', 'https://file4.batdongsan.com.vn/resize/200x200/2025/04/29/20250429160959-9bf9.jpg']</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Bán nhà hẻm xe hơi Quận 1 gần chợ Bến Thành 4x16m, 3 lầu ST giá 16.8 tỷ TL</t>
+          <t>Đẹp nhất, Hồ Biểu Chánh, Phú Nhuận - 82m2 - A4 - 4 tầng - hẻm kinh doanh, toàn biệt thự - 16,7 tỷ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>/ban-nha-rieng-duong-ben-chuong-duong-phuong-cau-kho-53/ban-hem-xe-hoi-quan-1-gan-cho-thanh-4x16m-3-lau-st-gia-16-8-ty-tl-pr44827272</t>
+          <t>/ban-nha-rieng-duong-ho-bieu-chanh-phuong-11-9-68/ep-nhat-phu-nhuan-82m2-a4-4-tang-hem-kinh-doanh-toan-biet-thu-16-7-ty-pr45655404</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>16,8 tỷ</t>
+          <t>16,7 tỷ</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>60,4 m²</t>
+          <t>82 m²</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>278,15 tr/m²</t>
+          <t>203,66 tr/m²</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Quận 1, Hồ Chí Minh</t>
+          <t>Q. Phú Nhuận (P. Phú Nhuận mới)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Bán nhà hẻm xe hơi Quận 1. Trên trục Bến Chương Dương - Trần Hưng Đạo - Nguyễn Văn Cừ khu vực thông thoáng thuận tiện sử dụng để ở và khai thác kinh doanh nhiều loại hình dịch vụ. Diện tích: 4 x 16m CN 60.4m² vuông vức. Nhà trệt 3 lầu sân thượng mới đẹp. Pháp lý chính chủ thuận tiện mua bán. Giá bán: 16,8 tỷ thương lượng. Liên hệ: 0937 865 *** Thanh Tùng để hỗ trợ xem nhà. Nhận tư vấn thủ tục pháp lý, ký gởi mua bán nhà phố quận trung tâm.</t>
+          <t>Đẹp nhất Hồ Biểu Chánh, P11. Phú Nhuận.DT: 82m² - sổ đẹp a4 - 4 tầng - hẻm kinh doanh, toàn biệt thự, ô tô tránh - 16,7 tỷ.- Khu hành chính Phú Nhuận, ngay trục Nguyễn Văn Trỗi đi vào, dân trí cao, sang trọng.0979 686 *** Duy Huỳnh trân trọng.</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>‎Nguyễn Thanh Tùng</t>
+          <t>‎Lê Huỳnh Duy</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>['https://file4.batdongsan.com.vn/crop/232x186/2025/12/17/20251217180612-9e3f_wm.jpg', 'https://file4.batdongsan.com.vn/crop/115x64/2025/12/17/20251217180612-4efb_wm.jpg', 'https://file4.batdongsan.com.vn/crop/115x64/2025/12/17/20251217180612-ee25_wm.jpg', 'https://file4.batdongsan.com.vn/resize/200x200/2024/06/05/20240605160845-51a5.jpg']</t>
+          <t>['https://file4.batdongsan.com.vn/crop/232x186/2026/05/02/20260502121725-5669_wm.jpg', 'https://file4.batdongsan.com.vn/crop/115x64/2026/05/02/20260502121726-37f3_wm.jpg', 'https://file4.batdongsan.com.vn/crop/115x64/2026/05/02/20260502121726-9ed5_wm.jpg', 'https://file4.batdongsan.com.vn/resize/200x200/2025/12/17/20251217090830-da98.jpg']</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Bán nhà riêng + CH mini 355m2 giá cực chất tại Phan Anh, Bình Trị Đông, Bình Tân, HCM</t>
+          <t>Bán nhà gần Nguyễn Duy Trinh tại đường 970, Phường Phú Hữu, Quận 9, 7.6 tỷ, 60m2, mới xây</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>/ban-nha-rieng-duong-phan-anh-phuong-binh-tri-dong-65/ban-ch-mini-355m2-gia-cuc-chat-tai-tan-hcm-pr44954094</t>
+          <t>/ban-nha-rieng-duong-970-phuong-phu-huu-2-61/ban-tai-uong-970-quan-9-7-6-ty-60m2-moi-xay-pr45608106</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>23,5 tỷ</t>
+          <t>7,6 tỷ</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>355 m²</t>
+          <t>60 m²</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>66,2 tr/m²</t>
+          <t>126,67 tr/m²</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Bình Tân, Hồ Chí Minh</t>
+          <t>Quận 9 (P. Long Trường mới)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Căn hộ mini + Nhà riêng Sân vườn cực chất với diện tích 355m², thiết kế 16PN, 16WC, hướng Đông, ban công Đông, nội thất đầy đủ như giường, tủ, bàn ghế, rất tiện cho cuộc sống hàng ngày.+ Pháp lý đầy đủ, sổ đỏ, sổ hồng. + Địa điểm lý tưởng cho những ai yêu thích không gian thoáng đãng và tiện nghi. + Thiết kế hiện đại, không gian sống thoải mái.Tiện ích xung quanh: + Bệnh viện chuyên khoa ngoại thần kinh quốc tế. + Công viên nước Đầm Sen, công viê...</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr"/>
+          <t>Được tọa lạc tại Đường 970, Phường Long Trường, Hồ Chí Minh (Quận 9, Hồ Chí Minh cũ), căn nhà riêng này có diện tích 60m² với thiết kế hiện đại và đầy đủ tiện nghi cơ bản.+ 4PN, 3WC, không gian rộng rãi và thoáng mát. + Mặt tiền 4.6m, đường vào rộng 8m, thuận tiện cho xe ô tô ra vào. + Pháp lý đầy đủ, đảm bảo an toàn cho giao dịch. + Khu vực yên tĩnh, thích hợp cho gia đình và sinh hoạt hàng ngày.Khu vực xung quanh.Gần công viên Phường Phú Hữu và...</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>‎Trung Trần</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
-          <t>['https://file4.batdongsan.com.vn/crop/232x186/2026/01/04/20260104224342-e35f_wm.jpg', 'https://file4.batdongsan.com.vn/crop/115x64/2026/01/04/20260104224343-2478_wm.jpg', 'https://file4.batdongsan.com.vn/crop/115x64/2026/01/04/20260104224343-9da7_wm.jpg']</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Chủ nhà đã cọc nhà to hơn, bán gấp căn trước tết. Căn 1 Trần Hưng Đạo, P1, Q 5</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>/ban-nha-rieng-duong-tran-hung-dao-phuong-1-15-57/chu-a-coc-to-hon-ban-gap-2-can-truoc-tet-can-1-ao-p1-q-5-can-2-xuan-soan-pr45141387</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>2,94 tỷ</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>18 m²</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>163,33 tr/m²</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Quận 5, Hồ Chí Minh</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>['https://file4.batdongsan.com.vn/crop/232x186/2026/02/05/20260205055658-b3f6_wm.jpg', 'https://staticfile.batdongsan.com.vn/images/Product/expired_icon.svg']</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Bán nhà 2 mặt tiền trước sau đường Hoàng Văn Thụ, Tân Bình, 118.4m2, đang cho thuê ổn định</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>/ban-nha-mat-pho-duong-hoang-van-thu-phuong-2-22-69/ban-gap-tan-binh-118-4m2-dang-cho-thue-on-dinh-2-tien-truoc-sau-pr44288165</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>33 tỷ</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>118,4 m²</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>278,72 tr/m²</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Tân Bình, Hồ Chí Minh</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>['https://file4.batdongsan.com.vn/crop/232x186/2025/10/15/20251015161947-2f49_wm.jpg', 'https://staticfile.batdongsan.com.vn/images/Product/expired_icon.svg']</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Bàu Cát P13 TB - HXH đỗ cửa, 3.65tỷ, ngộp bank giảm 500tr, 40.2m² nở hậu, không QH, sổ sẵn cc ngay</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>/ban-nha-rieng-duong-truong-cong-dinh-phuong-13-10-69/bau-cat-p13-tb-hxh-do-cua-3-65t-ngop-bank-giam-500tr-40-2m-no-hau-k-qh-so-san-cc-ngay-pr45000770</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>3,65 tỷ</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>40,2 m²</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>90,8 tr/m²</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Tân Bình, Hồ Chí Minh</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>['https://file4.batdongsan.com.vn/crop/232x186/2026/01/10/20260110185114-6c0d_wm.jpg', 'https://staticfile.batdongsan.com.vn/images/Product/expired_icon.svg']</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Đất lớn tuyệt đẹp tặng nguyên dãy trọ sát Gò Vấp, thu nhập 35tr/tháng, chỉ 22,5 tỷ còn thương lượng</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>/ban-nha-rieng-duong-vuon-lai-phuong-an-phu-dong-1-64/ban-dat-tang-day-tro-thu-nhap-35-trieu-thang-p-q-12-gan-go-vap-pr44956166</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>22,5 tỷ</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>346,3 m²</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>64,97 tr/m²</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Quận 12, Hồ Chí Minh</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>['https://staticfile.batdongsan.com.vn/images/Product/expired_icon.svg']</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Bán nhà phố 02 MT Làng Tăng Phú, trung tâm TP Thủ Đức (Xây dựng 02 căn riêng biệt). Sổ hồng riêng</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>/ban-nha-mat-pho-duong-lang-tang-phu-phuong-tang-nhon-phu-a-1-71/ban-02-mt-d-trung-tam-tp-thu-duc-xay-dung-02-can-rieng-biet-so-hong-rieng-pr44936070</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>10,8 tỷ</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>169 m²</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>63,9 tr/m²</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Thủ Đức, Hồ Chí Minh</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>['https://staticfile.batdongsan.com.vn/images/Product/expired_icon.svg']</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Siêu hiếm mặt tiền kinh doanh 5 tầng full nội thất 120m2 chỉ 12.488 tỷ</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>/ban-nha-mat-pho-duong-tan-thoi-nhat-6-phuong-tan-thoi-nhat-1-64/sieu-hiem-tien-kinh-doanh-5-tang-full-noi-that-120m2-chi-hon-12-ty-pr44908726</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>12,49 tỷ</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>118,9 m²</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>105,03 tr/m²</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Quận 12, Hồ Chí Minh</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>['https://staticfile.batdongsan.com.vn/images/Product/expired_icon.svg']</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Bán nhà chính chủ hẻm 637 Tỉnh Lộ 10 (HXH thông giữa đường Tỉnh lộ 10 và khu tên lửa)</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>/ban-nha-rieng-duong-tinh-lo-10-phuong-binh-tri-dong-b-65/ban-chinh-chu-hem-637-10-hxh-thong-giua-10-va-khu-ten-lua-pr44862053</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>5,6 tỷ</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>52,1 m²</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>107,49 tr/m²</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Bình Tân, Hồ Chí Minh</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>['https://staticfile.batdongsan.com.vn/images/Product/expired_icon.svg']</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Bán shophouse 131m2 chính chủ tại PARCSpring đường Nguyễn Duy Trinh, phường Bình Trưng</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>/ban-shophouse-nha-pho-thuong-mai-duong-nguyen-duy-trinh-phuong-binh-trung-dong-parcspring/ban-131m2-chinh-chu-tai-trung-pr44830357</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>8,55 tỷ</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>131 m²</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>65,27 tr/m²</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Quận 2, Hồ Chí Minh</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>['https://staticfile.batdongsan.com.vn/images/Product/expired_icon.svg']</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Bán giá rẻ hai nhà mặt tiền mặt phố tại Lý Chiêu Hoàng, Phường 10, Quận 6, TP. Hồ Chí Minh, 280m2</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>/ban-nha-mat-pho-duong-ly-chieu-hoang-phuong-10-4-58/ban-hai-tien-tai-10-quan-6-tp-ho-chi-minh-280m2-pr44516778</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>35 tỷ</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>280 m²</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>125 tr/m²</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Quận 6, Hồ Chí Minh</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>['https://staticfile.batdongsan.com.vn/images/Product/expired_icon.svg']</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Chính chủ bán nhanh CHDV HXH 5 tầng 80tr/th, gần khách sạn Đệ Nhất, Út Tịch, có thang máy, chỉ 16tỷ</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>/ban-nha-rieng-duong-hiep-nhat-phuong-4-20-69/chinh-chu-ban-nhanh-chdv-hxh-5-tang-80tr-th-gan-khach-san-de-ut-tich-co-thang-may-chi16-5ty-pr44674262</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>16 tỷ</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>90 m²</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>177,78 tr/m²</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Tân Bình, Hồ Chí Minh</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>['https://staticfile.batdongsan.com.vn/images/Product/expired_icon.svg']</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Cần bán gấp nhà 1 trệt 3 lầu đang có nguồn thu 45 triệu/ tháng ở Gò Vấp</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>/ban-nha-rieng-duong-quang-trung-phuong-10-8-67/can-ban-gap-1-tret-3-lau-dang-co-nguon-thu-45-trieu-thang-o-go-vap-pr44629859</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>11,5 tỷ</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>98,1 m²</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>117,23 tr/m²</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Gò Vấp, Hồ Chí Minh</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>['https://staticfile.batdongsan.com.vn/images/Product/expired_icon.svg']</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Duy nhất - nhà 3 tầng kiên cố, sẵn dòng tiền 30 triệu/tháng. Giá tốt nhất khu vực. Sẵn sổ sang tên</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>/ban-nha-rieng-duong-truong-chinh-phuong-13-10-69/duy-nhat-3-tang-kien-co-san-dong-tien-30-trieu-thang-gia-tot-nhat-khu-vuc-quan-tan-binh-pr44568972</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>16,48 tỷ</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>100,6 m²</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>163,82 tr/m²</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Tân Bình, Hồ Chí Minh</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>['https://staticfile.batdongsan.com.vn/images/Product/expired_icon.svg']</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Gấp! Chủ ngộp bank bán lỗ trước tết - nhà mới keng sát MT Âu Cơ, 3 lầu, full NT. Giá 4 tỷ 75</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>/ban-nha-rieng-duong-au-co-phuong-10-10-69/gap-chu-ngop-bank-ban-lo-truoc-tet-moi-keng-sat-mt-3-lau-full-nt-gia-4-ty-75-pr44610241</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>4,75 tỷ</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>35 m²</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>135,71 tr/m²</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Tân Bình, Hồ Chí Minh</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>['https://staticfile.batdongsan.com.vn/images/Product/expired_icon.svg']</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Bán gấp định cư nước ngoài - 4x14m vuông đẹp không lỗi - tiện cải tạo hoặc xây mới - 13.6tỷ TL mạnh</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>/ban-nha-mat-pho-duong-bau-cat-3-phuong-14-10-69/ban-gap-dinh-cu-nuoc-ngoai-4x14-vuong-dep-khong-loi-tien-cai-tao-hoac-xay-moi-13-6ty-tl-manh-pr44556728</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>13,6 tỷ</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>56 m²</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>242,86 tr/m²</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Tân Bình, Hồ Chí Minh</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>['https://staticfile.batdongsan.com.vn/images/Product/expired_icon.svg']</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Bán nhà 3 mặt tiền đường Huỳnh Tấn Phát, Q7 - sổ hồng hoàn công đầy đủ</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>/ban-nha-mat-pho-duong-huynh-tan-phat-phuong-phu-my-9-59/ban-3-tien-q7-so-hong-hoan-cong-day-du-pr44327628</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>82 tỷ</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>618,57 m²</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>132,56 tr/m²</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Quận 7, Hồ Chí Minh</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>['https://staticfile.batdongsan.com.vn/images/Product/expired_icon.svg']</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>MT Lê Đức Thọ DT thực 859.9m2 đoạn đẹp nhất đường. Giá tốt! Chủ rất thiện chí bán</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>/ban-nha-mat-pho-duong-le-duc-tho-phuong-13-8-67/mt-uc-gan-900m2-9x100-oan-ep-nhat-uong-gia-tot-chinh-chu-rat-thien-chi-ban-pr45155867</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>46 tỷ</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>859,9 m²</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>53,5 tr/m²</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Gò Vấp, Hồ Chí Minh</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>‎Nguyễn Minh Tuấn</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>['https://staticfile.batdongsan.com.vn/images/Product/expired_icon.svg', 'https://file4.batdongsan.com.vn/resize/200x200/2025/12/29/20251229151811-f03b.jpg']</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Bán nhà 344/2, Nguyễn Duy Dương, DT: 3.6m*12.5m. 43.2m2. Gía 6.7 tỷ Thương lượng</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>/ban-nha-rieng-duong-nguyen-duy-duong-phuong-9-9-62/ban-344-2-dt-4-6m-12-5m-43-2-m2-gia-6-7-ty-thuong-luong-pr45142553</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>6,7 tỷ</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>43,2 m²</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>155,09 tr/m²</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Quận 10, Hồ Chí Minh</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>‎Lê Trường Giang</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>['https://staticfile.batdongsan.com.vn/images/Product/expired_icon.svg', 'https://file4.batdongsan.com.vn/resize/200x200/2024/10/24/20241024154638-4995.jpg']</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Bán gấp nhà DT 7 x 16m hẻm xe hơi thông - Tỉnh Lộ 10 - Tân Tạo - Giá 7.55 tỷ</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>/ban-nha-rieng-duong-tinh-lo-10-phuong-tan-tao-65/ban-gap-dt-7-x-16-hem-xe-hoi-thong-10-gia-7-55-ty-pr45047881</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>7,55 tỷ</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>111 m²</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>68,02 tr/m²</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Bình Tân, Hồ Chí Minh</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>['https://file4.batdongsan.com.vn/crop/232x186/2026/01/17/20260117101354-c202_wm.jpg', 'https://staticfile.batdongsan.com.vn/images/Product/expired_icon.svg']</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Quá hiếm diện tích 100m2 - 2 tầng ngay gần Dương Thị Giang P. Tân Thới Nhất quận 12 khu 38ha</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>/ban-nha-rieng-duong-phan-van-hon-phuong-tan-thoi-nhat-1-64/qua-hiem-dien-tich-100m2-2-tang-ngay-gan-thi-giang-p-quan-12-khu-38ha-pr44921403</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>7,15 tỷ</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>100 m²</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>71,5 tr/m²</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Quận 12, Hồ Chí Minh</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>['https://file4.batdongsan.com.vn/crop/232x186/2025/12/29/20251229215407-ae6e_wm.jpg', 'https://staticfile.batdongsan.com.vn/images/Product/expired_icon.svg']</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Nhà mặt tiền Hòa Bình kế bên trường tiểu học Hòa Bình, tiện ở &amp; kinh doanh</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>/ban-nha-mat-pho-duong-hoa-binh-1-phuong-5-13-63/tien-ke-ben-truong-tieu-hoc-tien-o-kinh-doanh-pr44499212</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>15,6 tỷ</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>69,4 m²</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>224,78 tr/m²</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Quận 11, Hồ Chí Minh</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>['https://file4.batdongsan.com.vn/crop/232x186/2026/01/26/20260126084716-2679_wm.jpg', 'https://staticfile.batdongsan.com.vn/images/Product/expired_icon.svg']</t>
+          <t>['https://file4.batdongsan.com.vn/crop/232x186/2026/04/22/20260422174058-f784_wm.jpg', 'https://file4.batdongsan.com.vn/crop/115x64/2026/04/22/20260422174058-ff48_wm.jpg', 'https://file4.batdongsan.com.vn/crop/115x64/2026/04/22/20260422174058-046a_wm.jpg', 'https://file4.batdongsan.com.vn/resize/200x200/2026/04/21/20260421155801-88e9.jpg']</t>
         </is>
       </c>
     </row>
